--- a/docs/gantt.xlsx
+++ b/docs/gantt.xlsx
@@ -532,7 +532,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>в работе</t>
+          <t>сделано</t>
         </is>
       </c>
     </row>
@@ -557,7 +557,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>не начато</t>
+          <t>в работе</t>
         </is>
       </c>
     </row>

--- a/docs/gantt.xlsx
+++ b/docs/gantt.xlsx
@@ -557,7 +557,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>в работе</t>
+          <t>сделано</t>
         </is>
       </c>
     </row>
@@ -582,7 +582,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>не начато</t>
+          <t>в работе</t>
         </is>
       </c>
     </row>
